--- a/extenbooks/XS1001.xlsx
+++ b/extenbooks/XS1001.xlsx
@@ -450,14 +450,14 @@
   <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="61" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>XS1001 — Labor Share of National Income (Tonak 1984)</t>
+          <t>XS1001 — Labor Portion of Total Taxes (Tonak 1984, Table V)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Labor Share of National Income (Tonak 1984)</t>
+          <t>Labor Portion of Total Taxes (Tonak 1984, Table V)</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1292,85 +1292,85 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Labor share (W/NI) is computed as the ratio of wages and salaries received by workers to national income. Tonak allocates NIPA employee compensation between labor and non-labor using an income-proportional 'labor share' factor (Total labor income / Personal income). For 1964 this factor is 0.73. The resulting series covers 1952-1980 and appears in Chapter IV, Table II ('Calculation of Labor Share, 1952-80'). The labor share is also used as the allocation key for Group II taxes and Group II expenditures throughout the dissertation.</t>
+          <t>T7/T1 STUDY ANCHOR (WP-E review, 2026-07-01). XS1001-A is a verbatim digitization of the 'Labor' column of Tonak (1984) Chapter IV Table V, 'Labor and Non-Labor Portions of Total Taxes' (p.98): 1952 Labor = 34.58, 1980 Labor = 456.39 (billions of current USD). The source CSV Tonak1984_table_V_taxes_labor_nonlabor_1952_1980.csv reproduces Table V with 0/29 mismatches; independently corroborated against the HDARP extraction chunk_12. This external anchor (the study's own printed table, not the pipeline's own output) is what backs validation.reference_values.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables, Chapter IV Table II, p.92); chunk_001/full_transcription.md (Abstract, Table of Contents)</t>
+          <t>Tonak 1984, Table V, p.98 (Labor column)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Primary source: Tonak (1984) PhD Dissertation, New School for Social Research, Chapter IV Table II ('Calculation of Labor Share, 1952-80', p.92), covering 1952-1980 (28 annual observations). Underlying raw data from U.S. National Income and Product Accounts (NIPA). Table III ('Comparison of Labor Shares — Weisskopf and Tonak', p.93) provides cross-validation against Weisskopf's estimates. Per [internal-decision-record], the data_quality must be 'real_extracted' — values must be taken from HDARP-extracted Table II, not synthetically generated.</t>
+          <t>Labor share (W/NI) is computed as the ratio of wages and salaries received by workers to national income. Tonak allocates NIPA employee compensation between labor and non-labor using an income-proportional 'labor share' factor (Total labor income / Personal income). For 1964 this factor is 0.73. The resulting series covers 1952-1980 and appears in Chapter IV, Table II ('Calculation of Labor Share, 1952-80'). The labor share is also used as the allocation key for Group II taxes and Group II expenditures throughout the dissertation.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables p.v, Chapter IV Table II p.92, Table III p.93)</t>
+          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables, Chapter IV Table II, p.92); chunk_001/full_transcription.md (Abstract, Table of Contents)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>table_identification</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The primary table is Chapter IV Table II: 'Calculation of Labor Share, 1952-80' (p.92). A comparison table, Chapter IV Table III: 'Comparison of Labor Shares — Weisskopf and Tonak' (p.93), provides external validation. The labor share formula is also referenced in Chapter IV Table IV: 'Labor and Non-Labor Portions of Total Taxes — Selected Years' (p.95) and Table V: 'Labor and Non-Labor Portions of Total Taxes' (p.98). These tables are located in later HDARP chunks (not yet extracted in chunks 001-002).</t>
+          <t>Primary source: Tonak (1984) PhD Dissertation, New School for Social Research, Chapter IV Table II ('Calculation of Labor Share, 1952-80', p.92), covering 1952-1980 (28 annual observations). Underlying raw data from U.S. National Income and Product Accounts (NIPA). Table III ('Comparison of Labor Shares — Weisskopf and Tonak', p.93) provides cross-validation against Weisskopf's estimates. Per [internal-decision-record], the data_quality must be 'real_extracted' — values must be taken from HDARP-extracted Table II, not synthetically generated.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables pp.v-vi)</t>
+          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables p.v, Chapter IV Table II p.92, Table III p.93)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>table_identification</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Labor Share = Total labor income / Personal income. This ratio is applied to allocate Group II government expenditures and Group II personal taxes between workers and non-workers. Example value for 1964: 0.73 (cited in the 1987 Shaikh-Tonak paper's Appendix Table 1 footnote b).</t>
+          <t>The primary table is Chapter IV Table II: 'Calculation of Labor Share, 1952-80' (p.92). A comparison table, Chapter IV Table III: 'Comparison of Labor Shares — Weisskopf and Tonak' (p.93), provides external validation. The labor share formula is also referenced in Chapter IV Table IV: 'Labor and Non-Labor Portions of Total Taxes — Selected Years' (p.95) and Table V: 'Labor and Non-Labor Portions of Total Taxes' (p.98). These tables are located in later HDARP chunks (not yet extracted in chunks 001-002).</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_001/full_transcription.md (Abstract); 1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 footnote b)</t>
+          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables pp.v-vi)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Per [internal-decision-record] (No Synthetic Data Policy, 2026-05-03): XS1001 was previously identified as using synthetic data generated from summary statistics. The annual Table II values have not yet been extracted from the later HDARP chunks of Tonak (1984). Until a full HDARP extraction of Chapter IV (chunks covering pp.88-98) is completed, this series must be marked data_unavailable with an empty CSV. No np.random or benchmark-interpolation fills are permitted.</t>
+          <t>Labor Share = Total labor income / Personal income. This ratio is applied to allocate Group II government expenditures and Group II personal taxes between workers and non-workers. Example value for 1964: 0.73 (cited in the 1987 Shaikh-Tonak paper's Appendix Table 1 footnote b).</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[internal-decision-log]#[internal-decision-record]</t>
+          <t>1984_Tonak_State_Revenues/chunk_001/full_transcription.md (Abstract); 1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 footnote b)</t>
         </is>
       </c>
     </row>
@@ -1382,73 +1382,81 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The labor share concept in Tonak (1984) is defined as wages/national income following the labor theory of value framework, which differs from conventional national accounts definitions (e.g., BLS or BEA labor share). Tonak explicitly compares with Weisskopf's estimates (Chapter IV Table III, p.93), documenting methodological divergence. Users must not conflate this series with mainstream labor share measures.</t>
+          <t>Per [internal-decision-record] (No Synthetic Data Policy, 2026-05-03): XS1001 was previously identified as using synthetic data generated from summary statistics. The annual Table II values have not yet been extracted from the later HDARP chunks of Tonak (1984). Until a full HDARP extraction of Chapter IV (chunks covering pp.88-98) is completed, this series must be marked data_unavailable with an empty CSV. No np.random or benchmark-interpolation fills are permitted.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables, Chapter IV Table III p.93)</t>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cross_study_note</t>
+          <t>caveat</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The 1987 Shaikh-Tonak paper uses the same labor share methodology (citing 'Tonak 1984:Chap. IV; 1987') to allocate Group II expenditures and taxes. The 1964 labor share of 0.73 is directly confirmed in S&amp;T (1987) Appendix Table 1 footnote b. The labor share for XS1001 is therefore fully consistent with the XS1101/XS1102/XS1103 series from the 1987 paper.</t>
+          <t>The labor share concept in Tonak (1984) is defined as wages/national income following the labor theory of value framework, which differs from conventional national accounts definitions (e.g., BLS or BEA labor share). Tonak explicitly compares with Weisskopf's estimates (Chapter IV Table III, p.93), documenting methodological divergence. Users must not conflate this series with mainstream labor share measures.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1, footnotes b and d)</t>
+          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables, Chapter IV Table III p.93)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>cross_study_note</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The 1987 Shaikh-Tonak paper uses the same labor share methodology (citing 'Tonak 1984:Chap. IV; 1987') to allocate Group II expenditures and taxes. The 1964 labor share of 0.73 is directly confirmed in S&amp;T (1987) Appendix Table 1 footnote b. The labor share for XS1001 is therefore fully consistent with the XS1101/XS1102/XS1103 series from the 1987 paper.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1, footnotes b and d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>decision_reference</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[internal-decision-record] (No Synthetic Data Policy, 2026-05-03): XS1001 was explicitly named as one of five series with prohibited synthetic data. Remediation plan specifies: 'Extract real annual data from HDARP Table V.B (28 years available)'. Note — the registry entry references 'Table II' (labor share) while [internal-decision-record] references 'Table V.B' (which is an Appendix III table for surplus value data). The correct source table for labor share is Chapter IV Table II (p.92). Researcher should verify which specific table the HDARP extraction covers when the relevant chunks become available.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>[internal-decision-log]#[internal-decision-record]; 1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables)</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>VERBATIM QUOTES (top-level)</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>To obtain the portions of these expenditures directed towards labor, all of the items in this group are multiplied by the "labor share" (0.73 for 1964) except the item of Transportation which is also adjusted by the "Gas Share of Passenger Cars" (Tonak 1984:Chap. IV; Appendix II).</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Workers' share = (Total labor income / Personal income) × Group II total</t>
+          <t>To obtain the portions of these expenditures directed towards labor, all of the items in this group are multiplied by the "labor share" (0.73 for 1964) except the item of Transportation which is also adjusted by the "Gas Share of Passenger Cars" (Tonak 1984:Chap. IV; Appendix II).</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1457,37 +1465,38 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Workers' share = (Total labor income / Personal income) × Group II total</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>For rationale and procedures of "labor share method," see Tonak (1984: Chap. IV; 1987).</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Labor portion of total taxes from Tonak (1984) Chapter IV Table V ('Labor and Non-Labor Portions of Total Taxes'), 1952-1980, billions of current USD. This is the dollar amount of taxes attributed to labor, obtained by applying Tonak's labor share (total labor income / adjusted personal income, ~0.71-0.75, Table II) to Group II taxes and assigning Group I (social security) fully to labor. The data is the Table V 'labor_taxes' column, NOT the labor-share ratio itself.</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Annual data not yet extracted — later HDARP chunks (covering pp.88-98) required</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1504,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[internal-decision-record] prohibits synthetic fill; series is data_unavailable until HDARP extraction completes</t>
+          <t>Annual data not yet extracted — later HDARP chunks (covering pp.88-98) required</t>
         </is>
       </c>
     </row>
@@ -1503,23 +1512,23 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
+          <t>[internal-decision-record] prohibits synthetic fill; series is data_unavailable until HDARP extraction completes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Registry entry cites 'Table II' but [internal-decision-record] mentions 'Table V.B' — source table identity requires verification against the actual HDARP extraction</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>XS1002</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1536,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XS1101</t>
+          <t>XS1002</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1544,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XS1102</t>
+          <t>XS1101</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1552,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XS1103</t>
+          <t>XS1102</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1560,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S604</t>
+          <t>XS1103</t>
         </is>
       </c>
     </row>
@@ -1559,37 +1568,45 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
+          <t>S604</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>S605</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tonak_1984</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Tonak, Ertugrul Ahmet. 1984. 'A Conceptualization of State Revenues and Expenditures U.S.: 1952-1980.' PhD Dissertation, New School for Social Research. UMI Order Number 9414212.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Tonak_1984</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tonak, Ertugrul Ahmet. 1984. 'A Conceptualization of State Revenues and Expenditures U.S.: 1952-1980.' PhD Dissertation, New School for Social Research. UMI Order Number 9414212.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>ST_1987</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' In Robert Cherry et al. (eds.), The Imperiled Economy, Book I. New York: Union for Radical Political Economics, pp. 184-194.</t>
         </is>
@@ -1610,7 +1627,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1690,7 +1707,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1952": 34.58, "1980": 456.39}</t>
+          <t>{"1952": 34.58, "1960": 59.96, "1970": 151.39, "1980": 456.39}</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1743,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>share_series</t>
+          <t>dollar_series</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1001.xlsx
+++ b/extenbooks/XS1001.xlsx
@@ -994,7 +994,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>`data/source/external_studies/Tonak1984_table_V_taxes_labor_nonlabor_1952_1980.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_XS1001_labor_share_tonak1984.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1001_labor_share_tonak1984.py`.</t>
+          <t>`data/source/external_studies/Tonak1984_table_V_taxes_labor_nonlabor_1952_1980.csv` (copied from predecessor-build's ExternalSources). Loader: `code/L01_loaders/L01_XS1001_labor_share_tonak1984.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1001_labor_share_tonak1984.py`.</t>
         </is>
       </c>
     </row>
